--- a/tools/importer/reports/import-institucional-template.report.xlsx
+++ b/tools/importer/reports/import-institucional-template.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="326">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>acesso-informacao-hub</t>
   </si>
   <si>
-    <t>2026-07-19T11:37:34.004Z</t>
+    <t>2026-07-19T18:08:11.942Z</t>
   </si>
   <si>
     <t>PBIO | Acesso à Informação</t>
@@ -64,7 +64,7 @@
     <t>cartas-de-governanca-e-politicas-publicas.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","downloads-accordion","downloads-accordion"]</t>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion"]</t>
   </si>
   <si>
     <t>cartas-de-governanca-e-politicas-publicas</t>
@@ -73,7 +73,7 @@
     <t>institucional-anchor</t>
   </si>
   <si>
-    <t>2026-07-19T12:03:14.141Z</t>
+    <t>2026-07-19T18:51:18.970Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Políticas públicas</t>
@@ -85,13 +85,13 @@
     <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","downloads-accordion"]</t>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion"]</t>
   </si>
   <si>
     <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
   </si>
   <si>
-    <t>2026-07-19T12:03:20.187Z</t>
+    <t>2026-07-19T18:51:23.588Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Departamento Pessoal</t>
@@ -124,43 +124,46 @@
     <t>institucional.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","anchornav-sticky"]</t>
+  </si>
+  <si>
+    <t>institucional</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:50:31.700Z</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional</t>
+  </si>
+  <si>
+    <t>outras-informacoes.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion"]</t>
+  </si>
+  <si>
+    <t>outras-informacoes</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:51:34.502Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | outras informações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/outras-informacoes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas.report.json</t>
+  </si>
+  <si>
     <t>["hero-banner"]</t>
   </si>
   <si>
-    <t>institucional</t>
-  </si>
-  <si>
-    <t>2026-07-19T12:02:34.342Z</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/institucional</t>
-  </si>
-  <si>
-    <t>outras-informacoes.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion"]</t>
-  </si>
-  <si>
-    <t>outras-informacoes</t>
-  </si>
-  <si>
-    <t>2026-07-19T12:03:32.282Z</t>
-  </si>
-  <si>
-    <t>Petrobras Biocombustível | outras informações</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/outras-informacoes</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/acoes-e-programas.report.json</t>
-  </si>
-  <si>
     <t>acesso-a-informacao/acoes-e-programas</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:28.244Z</t>
+    <t>2026-07-19T18:09:08.079Z</t>
   </si>
   <si>
     <t>PBIO | Ações e Programas</t>
@@ -175,7 +178,7 @@
     <t>acesso-a-informacao/auditorias</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:57.040Z</t>
+    <t>2026-07-19T18:09:34.298Z</t>
   </si>
   <si>
     <t>PBIO | Auditorias</t>
@@ -187,118 +190,121 @@
     <t>acesso-a-informacao/convenios-e-transferencias.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","cards-content-panel-plain","embed"]</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/convenios-e-transferencias</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:10:02.479Z</t>
+  </si>
+  <si>
+    <t>PBIO | Convênios e Transferências</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/convenios-e-transferencias</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/dados-abertos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/dados-abertos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:10:07.611Z</t>
+  </si>
+  <si>
+    <t>PBIO | Dados Abertos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/dados-abertos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/empregados-publicos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/empregados-publicos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:10:12.316Z</t>
+  </si>
+  <si>
+    <t>PBIO | Empregados Públicos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/empregados-publicos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/informacoes-classificadas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/informacoes-classificadas</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:10:19.751Z</t>
+  </si>
+  <si>
+    <t>PBIO | Informações Classificadas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/informacoes-classificadas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:08:18.994Z</t>
+  </si>
+  <si>
+    <t>PBIO | Informações institucionais</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:10:24.855Z</t>
+  </si>
+  <si>
+    <t>PBIO | Licitações e Contratos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:11:04.467Z</t>
+  </si>
+  <si>
+    <t>PBIO | Participação Social</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/perguntas-frequentes.report.json</t>
+  </si>
+  <si>
     <t>["hero-banner","cards-content-panel-plain"]</t>
   </si>
   <si>
-    <t>acesso-a-informacao/convenios-e-transferencias</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:26.801Z</t>
-  </si>
-  <si>
-    <t>PBIO | Convênios e Transferências</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/convenios-e-transferencias</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/dados-abertos.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/dados-abertos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:32.633Z</t>
-  </si>
-  <si>
-    <t>PBIO | Dados Abertos</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/dados-abertos</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/empregados-publicos.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/empregados-publicos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:37.517Z</t>
-  </si>
-  <si>
-    <t>PBIO | Empregados Públicos</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/empregados-publicos</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/informacoes-classificadas.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/informacoes-classificadas</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:42.776Z</t>
-  </si>
-  <si>
-    <t>PBIO | Informações Classificadas</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/informacoes-classificadas</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/institucional.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/institucional</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:37:40.444Z</t>
-  </si>
-  <si>
-    <t>PBIO | Informações institucionais</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/institucional</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/licitacoes-e-contratos.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/licitacoes-e-contratos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:48.123Z</t>
-  </si>
-  <si>
-    <t>PBIO | Licitações e Contratos</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/participacao-social.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/participacao-social</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:40:30.299Z</t>
-  </si>
-  <si>
-    <t>PBIO | Participação Social</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/participacao-social</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/perguntas-frequentes.report.json</t>
-  </si>
-  <si>
     <t>acesso-a-informacao/perguntas-frequentes</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:07.933Z</t>
+    <t>2026-07-19T18:11:42.883Z</t>
   </si>
   <si>
     <t>PBIO | FAQ</t>
@@ -313,7 +319,7 @@
     <t>acesso-a-informacao/receitas-e-despesas</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:14.846Z</t>
+    <t>2026-07-19T18:11:48.263Z</t>
   </si>
   <si>
     <t>PBIO | Receitas e Despesas</t>
@@ -328,7 +334,7 @@
     <t>acesso-a-informacao/sancoes-administrativas</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:08.809Z</t>
+    <t>2026-07-19T18:12:39.553Z</t>
   </si>
   <si>
     <t>PBIO | Sanções Administrativas</t>
@@ -343,7 +349,7 @@
     <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:13.839Z</t>
+    <t>2026-07-19T18:12:46.874Z</t>
   </si>
   <si>
     <t>PBIO | SIC</t>
@@ -358,7 +364,7 @@
     <t>acesso-a-informacao/transparencia-e-prestacao-de-contas</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:30.075Z</t>
+    <t>2026-07-19T18:13:04.199Z</t>
   </si>
   <si>
     <t>PBIO | Transparência</t>
@@ -373,7 +379,7 @@
     <t>institucional/auditoria</t>
   </si>
   <si>
-    <t>2026-07-19T12:02:41.210Z</t>
+    <t>2026-07-19T18:50:38.808Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Auditoria</t>
@@ -388,7 +394,7 @@
     <t>institucional/licitacoes-contratos-e-aquisicao-de-bens</t>
   </si>
   <si>
-    <t>2026-07-19T12:02:48.575Z</t>
+    <t>2026-07-19T18:50:43.843Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Licitações</t>
@@ -400,13 +406,13 @@
     <t>institucional/orgaos-estatutarios.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","downloads-accordion","downloads-accordion","accordion-nested","downloads-accordion"]</t>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion","accordion-nested","downloads-accordion"]</t>
   </si>
   <si>
     <t>institucional/orgaos-estatutarios</t>
   </si>
   <si>
-    <t>2026-07-19T12:02:55.766Z</t>
+    <t>2026-07-19T18:51:01.368Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Órgãos</t>
@@ -418,10 +424,13 @@
     <t>institucional/relatorios-anuais-e-informacoes-financeiras.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion"]</t>
+  </si>
+  <si>
     <t>institucional/relatorios-anuais-e-informacoes-financeiras</t>
   </si>
   <si>
-    <t>2026-07-19T12:03:06.507Z</t>
+    <t>2026-07-19T18:51:10.498Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Informações financeiras</t>
@@ -439,7 +448,7 @@
     <t>acesso-a-informacao/acoes-e-programas/carta-de-servicos</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:32.926Z</t>
+    <t>2026-07-19T18:09:14.248Z</t>
   </si>
   <si>
     <t>PBIO | Carta de Serviços</t>
@@ -454,7 +463,7 @@
     <t>acesso-a-informacao/acoes-e-programas/governanca</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:39.033Z</t>
+    <t>2026-07-19T18:09:19.904Z</t>
   </si>
   <si>
     <t>PBIO | Governança</t>
@@ -469,7 +478,7 @@
     <t>acesso-a-informacao/acoes-e-programas/programas-finalisticos</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:44.911Z</t>
+    <t>2026-07-19T18:09:24.192Z</t>
   </si>
   <si>
     <t>PBIO | Programas Finalísticos</t>
@@ -484,7 +493,7 @@
     <t>acesso-a-informacao/acoes-e-programas/recursos-financeiros-renuncia-de-receitas</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:51.084Z</t>
+    <t>2026-07-19T18:09:29.314Z</t>
   </si>
   <si>
     <t>PBIO | Concessões de Recursos e Renúncias de Receitas</t>
@@ -499,7 +508,7 @@
     <t>acesso-a-informacao/auditorias/acoes-de-supervisao-controle-e-correicao</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:03.154Z</t>
+    <t>2026-07-19T18:09:39.512Z</t>
   </si>
   <si>
     <t>PBIO | Supervisão, Controle e correição</t>
@@ -514,7 +523,7 @@
     <t>acesso-a-informacao/auditorias/demonstracoes-financeiras</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:08.744Z</t>
+    <t>2026-07-19T18:09:45.061Z</t>
   </si>
   <si>
     <t>PBIO | Demonstrações Financeiras</t>
@@ -529,7 +538,7 @@
     <t>acesso-a-informacao/auditorias/prestacao-de-contas</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:15.224Z</t>
+    <t>2026-07-19T18:09:49.985Z</t>
   </si>
   <si>
     <t>PBIO | Prestação de Contas</t>
@@ -544,7 +553,7 @@
     <t>acesso-a-informacao/auditorias/relatorios-da-cgu</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:19.618Z</t>
+    <t>2026-07-19T18:09:55.342Z</t>
   </si>
   <si>
     <t>PBIO | Relatórios da CGU</t>
@@ -562,7 +571,7 @@
     <t>acesso-a-informacao/institucional/agenda-de-autoridades</t>
   </si>
   <si>
-    <t>2026-07-19T11:52:54.539Z</t>
+    <t>2026-07-19T18:08:31.770Z</t>
   </si>
   <si>
     <t>PBIO | Agenda de Autoridades</t>
@@ -577,7 +586,7 @@
     <t>acesso-a-informacao/institucional/atas</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:01.888Z</t>
+    <t>2026-07-19T18:08:38.770Z</t>
   </si>
   <si>
     <t>PBIO | Atas</t>
@@ -592,7 +601,7 @@
     <t>acesso-a-informacao/institucional/atos-normativos</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:07.463Z</t>
+    <t>2026-07-19T18:08:44.547Z</t>
   </si>
   <si>
     <t>PBIO | Atos normativos</t>
@@ -607,7 +616,7 @@
     <t>acesso-a-informacao/institucional/horario-de-atendimento</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:11.770Z</t>
+    <t>2026-07-19T18:08:50.865Z</t>
   </si>
   <si>
     <t>PBIO | Horário de Atendimento</t>
@@ -622,7 +631,7 @@
     <t>acesso-a-informacao/institucional/hospitalidades</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:16.176Z</t>
+    <t>2026-07-19T18:08:56.772Z</t>
   </si>
   <si>
     <t>PBIO | Hospitalidades Recebidas</t>
@@ -637,7 +646,7 @@
     <t>acesso-a-informacao/institucional/presentes</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:23.020Z</t>
+    <t>2026-07-19T18:09:02.139Z</t>
   </si>
   <si>
     <t>PBIO | Presentes Recebidos</t>
@@ -652,7 +661,7 @@
     <t>acesso-a-informacao/institucional/sobre</t>
   </si>
   <si>
-    <t>2026-07-19T11:37:47.432Z</t>
+    <t>2026-07-19T18:08:23.850Z</t>
   </si>
   <si>
     <t>PBIO | Quem Somos</t>
@@ -667,7 +676,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/aditivos</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:54.935Z</t>
+    <t>2026-07-19T18:10:30.653Z</t>
   </si>
   <si>
     <t>PBIO | Aditivos</t>
@@ -682,7 +691,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/contratos-de-transferencia-de-tecnologia</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:09.000Z</t>
+    <t>2026-07-19T18:10:46.205Z</t>
   </si>
   <si>
     <t>PBIO | Contratos de Transferência de Tecnologia</t>
@@ -697,7 +706,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/contratos</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:02.294Z</t>
+    <t>2026-07-19T18:10:39.222Z</t>
   </si>
   <si>
     <t>PBIO | Contratos</t>
@@ -709,10 +718,13 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/licitacoes.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","embed","cards-content-panel-plain"]</t>
+  </si>
+  <si>
     <t>acesso-a-informacao/licitacoes-e-contratos/licitacoes</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:17.478Z</t>
+    <t>2026-07-19T18:10:54.429Z</t>
   </si>
   <si>
     <t>PBIO | Licitações</t>
@@ -727,7 +739,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/patrocinios</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:22.984Z</t>
+    <t>2026-07-19T18:10:59.065Z</t>
   </si>
   <si>
     <t>PBIO | Patrocínios</t>
@@ -742,7 +754,7 @@
     <t>acesso-a-informacao/participacao-social/audiencias-publicas</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:35.859Z</t>
+    <t>2026-07-19T18:11:10.285Z</t>
   </si>
   <si>
     <t>PBIO | Audiências Públicas</t>
@@ -757,7 +769,7 @@
     <t>acesso-a-informacao/participacao-social/conferencias</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:40.486Z</t>
+    <t>2026-07-19T18:11:14.956Z</t>
   </si>
   <si>
     <t>PBIO | Conferências</t>
@@ -772,7 +784,7 @@
     <t>acesso-a-informacao/participacao-social/conselhos-e-orgaos-colegiados</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:45.720Z</t>
+    <t>2026-07-19T18:11:21.418Z</t>
   </si>
   <si>
     <t>PBIO | Conselhos e Órgãos Colegiados</t>
@@ -787,7 +799,7 @@
     <t>acesso-a-informacao/participacao-social/editais-de-chamamento-publico</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:50.831Z</t>
+    <t>2026-07-19T18:11:26.962Z</t>
   </si>
   <si>
     <t>PBIO | Editais de Chamamento Público</t>
@@ -802,7 +814,7 @@
     <t>acesso-a-informacao/participacao-social/outras-acoes</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:55.397Z</t>
+    <t>2026-07-19T18:11:33.474Z</t>
   </si>
   <si>
     <t>PBIO | Outras Ações</t>
@@ -817,7 +829,7 @@
     <t>acesso-a-informacao/participacao-social/ouvidoria</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:01.714Z</t>
+    <t>2026-07-19T18:11:37.931Z</t>
   </si>
   <si>
     <t>PBIO | Ouvidoria</t>
@@ -832,7 +844,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/alienacao-de-bens-imoveis</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:20.846Z</t>
+    <t>2026-07-19T18:11:53.860Z</t>
   </si>
   <si>
     <t>PBIO | Alienação de Bens Imóveis</t>
@@ -847,7 +859,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/aquisicao-de-bens</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:27.311Z</t>
+    <t>2026-07-19T18:12:00.489Z</t>
   </si>
   <si>
     <t>PBIO | Aquisição de Bens</t>
@@ -862,7 +874,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/diarias-e-passagens</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:32.931Z</t>
+    <t>2026-07-19T18:12:07.222Z</t>
   </si>
   <si>
     <t>PBIO | Diárias e Passagens</t>
@@ -880,7 +892,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/orcamento-de-investimento</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:39.094Z</t>
+    <t>2026-07-19T18:12:12.276Z</t>
   </si>
   <si>
     <t>PBIO | Orçamento de Investimento</t>
@@ -895,7 +907,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/politica-de-dividendos</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:45.080Z</t>
+    <t>2026-07-19T18:12:16.886Z</t>
   </si>
   <si>
     <t>PBIO | Política de Dividendos</t>
@@ -910,7 +922,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/politica-de-transacoes-com-partes-relacionadas</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:50.583Z</t>
+    <t>2026-07-19T18:12:22.872Z</t>
   </si>
   <si>
     <t>PBIO | Política de Transações</t>
@@ -925,7 +937,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/publicidade</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:56.011Z</t>
+    <t>2026-07-19T18:12:28.137Z</t>
   </si>
   <si>
     <t>PBIO | Publicidade</t>
@@ -940,7 +952,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/receitas</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:01.484Z</t>
+    <t>2026-07-19T18:12:34.788Z</t>
   </si>
   <si>
     <t>PBIO | Receitas</t>
@@ -955,7 +967,7 @@
     <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/balcoes-de-atendimento</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:20.110Z</t>
+    <t>2026-07-19T18:12:52.476Z</t>
   </si>
   <si>
     <t>PBIO | Atendimento</t>
@@ -970,7 +982,7 @@
     <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/estatisticas-do-sic</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:24.836Z</t>
+    <t>2026-07-19T18:12:58.202Z</t>
   </si>
   <si>
     <t>PBIO | Estatísticas do SIC</t>
@@ -1561,10 +1573,10 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1573,24 +1585,24 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1599,24 +1611,24 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1625,24 +1637,24 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1651,24 +1663,24 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1677,24 +1689,24 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1703,24 +1715,24 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1729,24 +1741,24 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1755,24 +1767,24 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1781,24 +1793,24 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1807,24 +1819,24 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1833,24 +1845,24 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1859,24 +1871,24 @@
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1885,24 +1897,24 @@
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1911,24 +1923,24 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1937,24 +1949,24 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1963,24 +1975,24 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1989,24 +2001,24 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -2015,24 +2027,24 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G25" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -2041,24 +2053,24 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G26" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2067,24 +2079,24 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G27" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -2093,24 +2105,24 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G28" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2119,24 +2131,24 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G29" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H29" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -2145,24 +2157,24 @@
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G30" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H30" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2171,24 +2183,24 @@
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G31" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H31" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2197,24 +2209,24 @@
         <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2223,24 +2235,24 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G33" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H33" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2249,24 +2261,24 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2275,24 +2287,24 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G35" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H35" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -2301,24 +2313,24 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G36" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2327,24 +2339,24 @@
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G37" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H37" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2353,24 +2365,24 @@
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H38" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2379,24 +2391,24 @@
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H39" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2405,24 +2417,24 @@
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H40" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="C41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2431,24 +2443,24 @@
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G41" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H41" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2457,24 +2469,24 @@
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G42" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H42" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2483,24 +2495,24 @@
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G43" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="C44" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2509,24 +2521,24 @@
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G44" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H44" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2535,24 +2547,24 @@
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G45" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H45" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2561,24 +2573,24 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G46" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H46" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -2587,24 +2599,24 @@
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G47" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H47" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2613,24 +2625,24 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G48" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H48" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2639,24 +2651,24 @@
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G49" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H49" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2665,24 +2677,24 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G50" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H50" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2691,24 +2703,24 @@
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G51" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H51" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C52" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2717,24 +2729,24 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G52" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H52" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="C53" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2743,24 +2755,24 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G53" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H53" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2769,24 +2781,24 @@
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G54" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H54" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B55" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C55" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2795,24 +2807,24 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G55" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="H55" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2821,24 +2833,24 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G56" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H56" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2847,24 +2859,24 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G57" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H57" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2873,24 +2885,24 @@
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G58" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H58" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C59" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2899,24 +2911,24 @@
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G59" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H59" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C60" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2925,24 +2937,24 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G60" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H60" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C61" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2951,13 +2963,13 @@
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G61" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H61" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
